--- a/03_Outputs/De_la_Paz/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/De_la_Paz/03_Ordenamiento/ordenamiento.xlsx
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E3" s="112">
-        <v>0.505738936610428</v>
+        <v>0.505738936610427</v>
       </c>
     </row>
     <row r="4">
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.505738936610428</v>
+        <v>0.505738936610427</v>
       </c>
     </row>
     <row r="4">
